--- a/outputs/question1/result1.xlsx
+++ b/outputs/question1/result1.xlsx
@@ -941,7 +941,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>1406.6411</v>
+        <v>1406.32986667</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -949,7 +949,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>1406.32986667</v>
+        <v>574.050516667</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -957,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>574.050516667</v>
+        <v>575.740616667</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -965,7 +965,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>575.740616667</v>
+        <v>576.471216667</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -973,7 +973,7 @@
         <v>144</v>
       </c>
       <c r="B6" s="2">
-        <v>576.471216667</v>
+        <v>576.640016667</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -981,7 +981,7 @@
         <v>98</v>
       </c>
       <c r="B7" s="2">
-        <v>576.640016667</v>
+        <v>577.8597</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -989,7 +989,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>577.8597</v>
+        <v>577.993866667</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -997,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>577.993866667</v>
+        <v>577.82805</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1005,7 +1005,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>577.82805</v>
+        <v>580.41545</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1013,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>580.41545</v>
+        <v>582.514016667</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1021,7 +1021,7 @@
         <v>99</v>
       </c>
       <c r="B12" s="2">
-        <v>582.514016667</v>
+        <v>583.07405</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1029,7 +1029,7 @@
         <v>100</v>
       </c>
       <c r="B13" s="2">
-        <v>583.07405</v>
+        <v>584.204916667</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1037,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="2">
-        <v>584.204916667</v>
+        <v>585.439783333</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1045,7 +1045,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>585.439783333</v>
+        <v>586.14475</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1053,7 +1053,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="2">
-        <v>586.14475</v>
+        <v>586.320766667</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1061,7 +1061,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>586.320766667</v>
+        <v>586.4253</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1069,7 +1069,7 @@
         <v>101</v>
       </c>
       <c r="B18" s="2">
-        <v>586.4253</v>
+        <v>586.8496</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1077,7 +1077,7 @@
         <v>102</v>
       </c>
       <c r="B19" s="2">
-        <v>586.8496</v>
+        <v>587.821016667</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1085,7 +1085,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="2">
-        <v>587.821016667</v>
+        <v>589.547566667</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1093,7 +1093,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="2">
-        <v>589.547566667</v>
+        <v>590.813466667</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1101,7 +1101,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="2">
-        <v>590.813466667</v>
+        <v>590.213116667</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1109,7 +1109,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="2">
-        <v>590.213116667</v>
+        <v>591.066266667</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1117,7 +1117,7 @@
         <v>103</v>
       </c>
       <c r="B24" s="2">
-        <v>591.066266667</v>
+        <v>593.367833333</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1125,7 +1125,7 @@
         <v>104</v>
       </c>
       <c r="B25" s="2">
-        <v>593.367833333</v>
+        <v>593.659683333</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1133,7 +1133,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="2">
-        <v>593.659683333</v>
+        <v>592.786383333</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1141,7 +1141,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="2">
-        <v>592.786383333</v>
+        <v>593.337866667</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1149,7 +1149,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="2">
-        <v>593.337866667</v>
+        <v>596.675766667</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1157,7 +1157,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="2">
-        <v>596.675766667</v>
+        <v>597.78025</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1165,7 +1165,7 @@
         <v>105</v>
       </c>
       <c r="B30" s="2">
-        <v>597.78025</v>
+        <v>595.1625</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1173,7 +1173,7 @@
         <v>106</v>
       </c>
       <c r="B31" s="2">
-        <v>595.1625</v>
+        <v>590.6065</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1181,7 +1181,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="2">
-        <v>590.6065</v>
+        <v>589.485183333</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1189,7 +1189,7 @@
         <v>23</v>
       </c>
       <c r="B33" s="2">
-        <v>589.485183333</v>
+        <v>578.45545</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1197,7 +1197,7 @@
         <v>24</v>
       </c>
       <c r="B34" s="2">
-        <v>578.45545</v>
+        <v>1383.65978333</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1205,7 +1205,7 @@
         <v>25</v>
       </c>
       <c r="B35" s="2">
-        <v>1383.65978333</v>
+        <v>591.1402</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1213,7 +1213,7 @@
         <v>107</v>
       </c>
       <c r="B36" s="2">
-        <v>591.1402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1293,7 +1293,7 @@
         <v>32</v>
       </c>
       <c r="B46" s="2">
-        <v>0</v>
+        <v>0.000100847772411</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1301,7 +1301,7 @@
         <v>33</v>
       </c>
       <c r="B47" s="2">
-        <v>0.000100847754066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1461,7 +1461,7 @@
         <v>116</v>
       </c>
       <c r="B67" s="2">
-        <v>0</v>
+        <v>575.170916667</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1469,7 +1469,7 @@
         <v>46</v>
       </c>
       <c r="B68" s="2">
-        <v>575.170916667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1485,7 +1485,7 @@
         <v>48</v>
       </c>
       <c r="B70" s="2">
-        <v>0</v>
+        <v>179.277046896</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1493,7 +1493,7 @@
         <v>49</v>
       </c>
       <c r="B71" s="2">
-        <v>179.277046896</v>
+        <v>520.124516667</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1501,7 +1501,7 @@
         <v>117</v>
       </c>
       <c r="B72" s="2">
-        <v>520.124516667</v>
+        <v>486.4029</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1509,7 +1509,7 @@
         <v>118</v>
       </c>
       <c r="B73" s="2">
-        <v>486.4029</v>
+        <v>480.41245</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1517,7 +1517,7 @@
         <v>50</v>
       </c>
       <c r="B74" s="2">
-        <v>480.41245</v>
+        <v>485.3</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1525,7 +1525,7 @@
         <v>51</v>
       </c>
       <c r="B75" s="2">
-        <v>485.3</v>
+        <v>488.606966667</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1533,7 +1533,7 @@
         <v>52</v>
       </c>
       <c r="B76" s="2">
-        <v>488.606966667</v>
+        <v>498.270733333</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1541,7 +1541,7 @@
         <v>53</v>
       </c>
       <c r="B77" s="2">
-        <v>498.270733333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1645,7 +1645,7 @@
         <v>123</v>
       </c>
       <c r="B90" s="2">
-        <v>0</v>
+        <v>112.089866667</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1653,7 +1653,7 @@
         <v>124</v>
       </c>
       <c r="B91" s="2">
-        <v>112.089866667</v>
+        <v>266.732693621</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1661,7 +1661,7 @@
         <v>62</v>
       </c>
       <c r="B92" s="2">
-        <v>266.732693621</v>
+        <v>197.523516667</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1669,7 +1669,7 @@
         <v>63</v>
       </c>
       <c r="B93" s="2">
-        <v>197.523516667</v>
+        <v>244.814033333</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
         <v>64</v>
       </c>
       <c r="B94" s="2">
-        <v>244.814033333</v>
+        <v>295.534616667</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1685,7 +1685,7 @@
         <v>65</v>
       </c>
       <c r="B95" s="2">
-        <v>295.534616667</v>
+        <v>345.7775</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1693,7 +1693,7 @@
         <v>126</v>
       </c>
       <c r="B96" s="2">
-        <v>345.7775</v>
+        <v>394.931483333</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1701,7 +1701,7 @@
         <v>125</v>
       </c>
       <c r="B97" s="2">
-        <v>394.931483333</v>
+        <v>445.43165</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1709,7 +1709,7 @@
         <v>66</v>
       </c>
       <c r="B98" s="2">
-        <v>445.43165</v>
+        <v>495.696583333</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1717,7 +1717,7 @@
         <v>67</v>
       </c>
       <c r="B99" s="2">
-        <v>495.696583333</v>
+        <v>547.11905</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1725,7 +1725,7 @@
         <v>68</v>
       </c>
       <c r="B100" s="2">
-        <v>547.11905</v>
+        <v>599.985433333</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1733,7 +1733,7 @@
         <v>69</v>
       </c>
       <c r="B101" s="2">
-        <v>599.985433333</v>
+        <v>635.42975</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1741,7 +1741,7 @@
         <v>127</v>
       </c>
       <c r="B102" s="2">
-        <v>635.42975</v>
+        <v>660.830683333</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1749,7 +1749,7 @@
         <v>128</v>
       </c>
       <c r="B103" s="2">
-        <v>660.830683333</v>
+        <v>702.036933333</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1757,7 +1757,7 @@
         <v>70</v>
       </c>
       <c r="B104" s="2">
-        <v>702.036933333</v>
+        <v>738.065783333</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1765,7 +1765,7 @@
         <v>71</v>
       </c>
       <c r="B105" s="2">
-        <v>738.065783333</v>
+        <v>775.944716667</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1773,7 +1773,7 @@
         <v>72</v>
       </c>
       <c r="B106" s="2">
-        <v>775.944716667</v>
+        <v>826.08325</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1781,7 +1781,7 @@
         <v>73</v>
       </c>
       <c r="B107" s="2">
-        <v>826.08325</v>
+        <v>762.4228</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1789,7 +1789,7 @@
         <v>141</v>
       </c>
       <c r="B108" s="2">
-        <v>762.4228</v>
+        <v>636.982616667</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1797,7 +1797,7 @@
         <v>140</v>
       </c>
       <c r="B109" s="2">
-        <v>636.982616667</v>
+        <v>531.89405</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1805,7 +1805,7 @@
         <v>74</v>
       </c>
       <c r="B110" s="2">
-        <v>531.89405</v>
+        <v>678.830533333</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1813,7 +1813,7 @@
         <v>75</v>
       </c>
       <c r="B111" s="2">
-        <v>678.830533333</v>
+        <v>686.2685</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1821,7 +1821,7 @@
         <v>76</v>
       </c>
       <c r="B112" s="2">
-        <v>686.2685</v>
+        <v>696.504383333</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1829,7 +1829,7 @@
         <v>77</v>
       </c>
       <c r="B113" s="2">
-        <v>696.504383333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1925,7 +1925,7 @@
         <v>85</v>
       </c>
       <c r="B125" s="2">
-        <v>0</v>
+        <v>715.868916667</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1933,7 +1933,7 @@
         <v>135</v>
       </c>
       <c r="B126" s="2">
-        <v>715.868916667</v>
+        <v>717.005116667</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1941,7 +1941,7 @@
         <v>134</v>
       </c>
       <c r="B127" s="2">
-        <v>717.005116667</v>
+        <v>720.1603</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1949,7 +1949,7 @@
         <v>86</v>
       </c>
       <c r="B128" s="2">
-        <v>720.1603</v>
+        <v>717.054866667</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1957,7 +1957,7 @@
         <v>87</v>
       </c>
       <c r="B129" s="2">
-        <v>717.054866667</v>
+        <v>720.445966667</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1965,7 +1965,7 @@
         <v>88</v>
       </c>
       <c r="B130" s="2">
-        <v>720.445966667</v>
+        <v>738.134716667</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1973,7 +1973,7 @@
         <v>89</v>
       </c>
       <c r="B131" s="2">
-        <v>738.134716667</v>
+        <v>671.693566667</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1981,7 +1981,7 @@
         <v>133</v>
       </c>
       <c r="B132" s="2">
-        <v>671.693566667</v>
+        <v>1393.79031667</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1989,7 +1989,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="2">
-        <v>1393.79031667</v>
+        <v>1384.8989</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -1997,7 +1997,7 @@
         <v>90</v>
       </c>
       <c r="B134" s="2">
-        <v>1384.8989</v>
+        <v>568.82605</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2005,7 +2005,7 @@
         <v>91</v>
       </c>
       <c r="B135" s="2">
-        <v>568.82605</v>
+        <v>1396.98855</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2013,7 +2013,7 @@
         <v>92</v>
       </c>
       <c r="B136" s="2">
-        <v>1396.98855</v>
+        <v>1397.75986667</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2021,7 +2021,7 @@
         <v>93</v>
       </c>
       <c r="B137" s="2">
-        <v>1397.75986667</v>
+        <v>1400.08076667</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2029,7 +2029,7 @@
         <v>131</v>
       </c>
       <c r="B138" s="2">
-        <v>1400.08076667</v>
+        <v>1399.87376667</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2037,7 +2037,7 @@
         <v>130</v>
       </c>
       <c r="B139" s="2">
-        <v>1399.87376667</v>
+        <v>1234.49681667</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2045,7 +2045,7 @@
         <v>94</v>
       </c>
       <c r="B140" s="2">
-        <v>1234.49681667</v>
+        <v>1402.69196667</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2053,7 +2053,7 @@
         <v>95</v>
       </c>
       <c r="B141" s="2">
-        <v>1402.69196667</v>
+        <v>1403.66351667</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2061,7 +2061,7 @@
         <v>96</v>
       </c>
       <c r="B142" s="2">
-        <v>1403.66351667</v>
+        <v>1404.94871667</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2069,7 +2069,7 @@
         <v>97</v>
       </c>
       <c r="B143" s="2">
-        <v>1404.94871667</v>
+        <v>573.176833333</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2077,7 +2077,7 @@
         <v>129</v>
       </c>
       <c r="B144" s="2">
-        <v>573.176833333</v>
+        <v>574.120983333</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="14" customHeight="1" x14ac:dyDescent="0.25">
@@ -2085,7 +2085,7 @@
         <v>150</v>
       </c>
       <c r="B145" s="2">
-        <v>574.120983333</v>
+        <v>1406.6411</v>
       </c>
     </row>
   </sheetData>
@@ -2149,7 +2149,7 @@
         <v>833.333333333</v>
       </c>
       <c r="C3" s="5">
-        <v>5947.41964915</v>
+        <v>6365.84109915</v>
       </c>
       <c r="E3" s="5">
         <v>8550</v>
@@ -2160,10 +2160,10 @@
         <v>146</v>
       </c>
       <c r="B4" s="5">
-        <v>3954.63083023</v>
+        <v>4787.96416356</v>
       </c>
       <c r="C4" s="5">
-        <v>2121.41843333</v>
+        <v>1702.99698333</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="5" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
@@ -2171,7 +2171,7 @@
         <v>147</v>
       </c>
       <c r="B5" s="5">
-        <v>6119.36851029</v>
+        <v>5286.03517695</v>
       </c>
       <c r="C5" s="5">
         <v>91.1013833333</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="5">
-        <v>5068.68685</v>
+        <v>5780.13188333</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="5" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.35">
@@ -2196,7 +2196,7 @@
         <v>8166.66666667</v>
       </c>
       <c r="C7" s="5">
-        <v>3571.31315</v>
+        <v>2859.86811667</v>
       </c>
     </row>
   </sheetData>
